--- a/ig/nr-add-vs-cs-to-id/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
+++ b/ig/nr-add-vs-cs-to-id/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:49:03+00:00</t>
+    <t>2024-01-29T09:55:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-vs-cs-to-id/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
+++ b/ig/nr-add-vs-cs-to-id/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
   <si>
     <t>Property</t>
   </si>
@@ -30,12 +30,6 @@
     <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-profession</t>
   </si>
   <si>
-    <t>Identifier</t>
-  </si>
-  <si>
-    <t>id: Uniform Resource Identifier (URI)#urn:oid: 2.16.840.1.113883.2.8.1.3.23</t>
-  </si>
-  <si>
     <t>Version</t>
   </si>
   <si>
@@ -69,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:55:21+00:00</t>
+    <t>2024-01-29T12:33:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -352,10 +346,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -378,28 +372,20 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" t="s" s="2">
-        <v>25</v>
-      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>27</v>
-      </c>
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -418,28 +404,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -458,28 +444,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -498,28 +484,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -538,28 +524,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/ig/nr-add-vs-cs-to-id/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
+++ b/ig/nr-add-vs-cs-to-id/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T12:33:53+00:00</t>
+    <t>2024-01-29T12:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-vs-cs-to-id/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
+++ b/ig/nr-add-vs-cs-to-id/ValueSet-fr-core-vs-practitioner-role-profession.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T12:36:14+00:00</t>
+    <t>2024-01-29T12:40:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
